--- a/Result/profitability/4933.xlsx
+++ b/Result/profitability/4933.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-3.43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.92125</v>
+        <v>0.8912500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>22.7325</v>
+        <v>22.7025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3574999999999999</v>
+        <v>0.2499999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.81125</v>
+        <v>13.90125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0.48125</v>
+        <v>0.32125</v>
       </c>
       <c r="N4" t="n">
-        <v>12.0325</v>
+        <v>11.43625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>8.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.27</v>
+        <v>1.5025</v>
       </c>
       <c r="N5" t="n">
-        <v>11.75</v>
+        <v>11.6025</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.65125</v>
+        <v>1.48125</v>
       </c>
       <c r="N6" t="n">
-        <v>10.625</v>
+        <v>10.71125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.40875</v>
+        <v>1.28875</v>
       </c>
       <c r="N7" t="n">
-        <v>8.92375</v>
+        <v>9.2325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.34</v>
       </c>
       <c r="M8" t="n">
-        <v>1.33</v>
+        <v>1.21875</v>
       </c>
       <c r="N8" t="n">
-        <v>7.691249999999998</v>
+        <v>7.4725</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>1.2775</v>
       </c>
       <c r="N9" t="n">
-        <v>5.72375</v>
+        <v>5.723750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9322,6 +9322,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>681</v>
+      </c>
+      <c r="D71" t="n">
+        <v>469</v>
+      </c>
+      <c r="E71" t="n">
+        <v>212</v>
+      </c>
+      <c r="F71" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="G71" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>14.61%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>14</v>
+      </c>
+      <c r="J71" t="n">
+        <v>113</v>
+      </c>
+      <c r="K71" t="n">
+        <v>83</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.47625</v>
+      </c>
+      <c r="N71" t="n">
+        <v>31.6875</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-0.8899999999999999</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-0.468421052631579</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.05314303067112058</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-2.188235294117647</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.03646477132262049</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
